--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
@@ -453,7 +453,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -621,6 +621,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -630,7 +633,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -797,6 +800,9 @@
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>1166205.1375903317</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
               </c:numCache>
@@ -840,7 +846,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1008,6 +1014,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1017,7 +1026,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1185,6 +1194,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>1645486.3953516721</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1717515.4217862517</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1227,7 +1239,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1395,6 +1407,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1404,7 +1419,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1572,6 +1587,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>479281.25776134036</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>551310.28419591999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1593,11 +1611,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="345168128"/>
-        <c:axId val="345170304"/>
+        <c:axId val="522884992"/>
+        <c:axId val="523509760"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="345168128"/>
+        <c:axId val="522884992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1640,14 +1658,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="345170304"/>
+        <c:crossAx val="523509760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="345170304"/>
+        <c:axId val="523509760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1698,7 +1716,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="345168128"/>
+        <c:crossAx val="522884992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1889,7 +1907,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2057,6 +2075,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>-15847.849901360847</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-20790.629041221724</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,8 +2092,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="353742208"/>
-        <c:axId val="353739520"/>
+        <c:axId val="528433152"/>
+        <c:axId val="528419072"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2097,7 +2118,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2265,6 +2286,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2274,7 +2298,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="56"/>
+                <c:ptCount val="57"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2442,6 +2466,9 @@
                 </c:pt>
                 <c:pt idx="55">
                   <c:v>4.8240952148437497</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.0477412109374997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2458,11 +2485,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="353731712"/>
-        <c:axId val="353733632"/>
+        <c:axId val="523652096"/>
+        <c:axId val="528416768"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="353731712"/>
+        <c:axId val="523652096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2505,14 +2532,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="353733632"/>
+        <c:crossAx val="528416768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="353733632"/>
+        <c:axId val="528416768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2563,12 +2590,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="353731712"/>
+        <c:crossAx val="523652096"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="353739520"/>
+        <c:axId val="528419072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2605,12 +2632,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="353742208"/>
+        <c:crossAx val="528433152"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="353742208"/>
+        <c:axId val="528433152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2619,7 +2646,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="353739520"/>
+        <c:crossAx val="528419072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3028,7 +3055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5505,6 +5532,44 @@
         <v>91803.844257618461</v>
       </c>
     </row>
+    <row r="59" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A59" s="14">
+        <v>46022</v>
+      </c>
+      <c r="B59" s="15">
+        <v>5.0477412109374997</v>
+      </c>
+      <c r="C59" s="15">
+        <v>31.129999160000001</v>
+      </c>
+      <c r="D59" s="16">
+        <v>25.866548769817285</v>
+      </c>
+      <c r="E59" s="16">
+        <v>-20790.629041221724</v>
+      </c>
+      <c r="F59" s="17">
+        <v>-4118.7985224306603</v>
+      </c>
+      <c r="G59" s="17">
+        <v>317948.34192566201</v>
+      </c>
+      <c r="H59" s="17">
+        <v>1604920.9484874115</v>
+      </c>
+      <c r="I59" s="17">
+        <v>1166205.1375903317</v>
+      </c>
+      <c r="J59" s="17">
+        <v>1717515.4217862517</v>
+      </c>
+      <c r="K59" s="17">
+        <v>551310.28419591999</v>
+      </c>
+      <c r="L59" s="16">
+        <v>112594.47329884018</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,10 +70,6 @@
   </si>
   <si>
     <t>回收资金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -453,7 +449,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -624,6 +620,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -633,7 +632,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -803,6 +802,9 @@
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
                 <c:pt idx="56">
+                  <c:v>1166205.1375903317</c:v>
+                </c:pt>
+                <c:pt idx="57">
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
               </c:numCache>
@@ -846,7 +848,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1017,6 +1019,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1026,7 +1031,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1197,6 +1202,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>1717515.4217862517</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1757714.1522899114</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1239,7 +1247,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1410,6 +1418,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1419,7 +1430,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1590,6 +1601,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>551310.28419591999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>591509.01469957968</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1611,11 +1625,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="522884992"/>
-        <c:axId val="523509760"/>
+        <c:axId val="378314112"/>
+        <c:axId val="378322944"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="522884992"/>
+        <c:axId val="378314112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1658,14 +1672,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523509760"/>
+        <c:crossAx val="378322944"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="523509760"/>
+        <c:axId val="378322944"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1716,7 +1730,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="522884992"/>
+        <c:crossAx val="378314112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1907,7 +1921,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2078,6 +2092,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>-20790.629041221724</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-22659.73697994119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2092,8 +2109,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="528433152"/>
-        <c:axId val="528419072"/>
+        <c:axId val="616520704"/>
+        <c:axId val="616519168"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2118,7 +2135,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2289,6 +2306,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2298,7 +2318,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="57"/>
+                <c:ptCount val="58"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2469,6 +2489,9 @@
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>5.0477412109374997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.1741728515625001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2485,11 +2508,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="523652096"/>
-        <c:axId val="528416768"/>
+        <c:axId val="379840384"/>
+        <c:axId val="614387072"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="523652096"/>
+        <c:axId val="379840384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2532,14 +2555,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528416768"/>
+        <c:crossAx val="614387072"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="528416768"/>
+        <c:axId val="614387072"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2590,12 +2613,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="523652096"/>
+        <c:crossAx val="379840384"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="528419072"/>
+        <c:axId val="616519168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2632,12 +2655,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="528433152"/>
+        <c:crossAx val="616520704"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="528433152"/>
+        <c:axId val="616520704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2646,7 +2669,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="528419072"/>
+        <c:crossAx val="616519168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3055,7 +3078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3132,7 +3155,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3184,13 +3207,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>13</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3202,10 +3225,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" s="26" t="s">
         <v>15</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5568,6 +5591,44 @@
       </c>
       <c r="L59" s="16">
         <v>112594.47329884018</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A60" s="14">
+        <v>46052</v>
+      </c>
+      <c r="B60" s="15">
+        <v>5.1741728515625001</v>
+      </c>
+      <c r="C60" s="15">
+        <v>31.709999079999999</v>
+      </c>
+      <c r="D60" s="16">
+        <v>25.973356806597167</v>
+      </c>
+      <c r="E60" s="16">
+        <v>-22659.73697994119</v>
+      </c>
+      <c r="F60" s="17">
+        <v>-4379.393118476587</v>
+      </c>
+      <c r="G60" s="17">
+        <v>313568.9488071854</v>
+      </c>
+      <c r="H60" s="17">
+        <v>1622459.94201113</v>
+      </c>
+      <c r="I60" s="17">
+        <v>1166205.1375903317</v>
+      </c>
+      <c r="J60" s="17">
+        <v>1757714.1522899114</v>
+      </c>
+      <c r="K60" s="17">
+        <v>591509.01469957968</v>
+      </c>
+      <c r="L60" s="16">
+        <v>135254.21027878136</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,6 +70,10 @@
   </si>
   <si>
     <t>回收资金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -449,7 +453,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -623,6 +627,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -632,7 +639,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -805,6 +812,9 @@
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
                 <c:pt idx="57">
+                  <c:v>1166205.1375903317</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
               </c:numCache>
@@ -848,7 +858,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1022,6 +1032,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1031,7 +1044,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1205,6 +1218,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>1757714.1522899114</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>1740735.6492126763</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1247,7 +1263,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1421,6 +1437,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1430,7 +1449,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1604,6 +1623,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>591509.01469957968</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>574530.51162234461</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1625,11 +1647,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="378314112"/>
-        <c:axId val="378322944"/>
+        <c:axId val="403014400"/>
+        <c:axId val="403017728"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="378314112"/>
+        <c:axId val="403014400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1672,14 +1694,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378322944"/>
+        <c:crossAx val="403017728"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="378322944"/>
+        <c:axId val="403017728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1730,7 +1752,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378314112"/>
+        <c:crossAx val="403014400"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1921,7 +1943,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2095,6 +2117,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>-22659.73697994119</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-21765.21580417292</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2109,8 +2134,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="616520704"/>
-        <c:axId val="616519168"/>
+        <c:axId val="474839296"/>
+        <c:axId val="474837376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2135,7 +2160,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2309,6 +2334,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2318,7 +2346,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="58"/>
+                <c:ptCount val="59"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2492,6 +2520,9 @@
                 </c:pt>
                 <c:pt idx="57">
                   <c:v>5.1741728515625001</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.1200268554687502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2508,11 +2539,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="379840384"/>
-        <c:axId val="614387072"/>
+        <c:axId val="474810240"/>
+        <c:axId val="474829184"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="379840384"/>
+        <c:axId val="474810240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2555,14 +2586,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="614387072"/>
+        <c:crossAx val="474829184"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="614387072"/>
+        <c:axId val="474829184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2613,12 +2644,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="379840384"/>
+        <c:crossAx val="474810240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="616519168"/>
+        <c:axId val="474837376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2655,12 +2686,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="616520704"/>
+        <c:crossAx val="474839296"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="616520704"/>
+        <c:axId val="474839296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2669,7 +2700,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="616519168"/>
+        <c:crossAx val="474837376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3078,7 +3109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3155,7 +3186,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3207,13 +3238,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R3" s="26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3225,10 +3256,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5629,6 +5660,44 @@
       </c>
       <c r="L60" s="16">
         <v>135254.21027878136</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A61" s="14">
+        <v>46080</v>
+      </c>
+      <c r="B61" s="15">
+        <v>5.1200268554687502</v>
+      </c>
+      <c r="C61" s="15">
+        <v>31.549999239999998</v>
+      </c>
+      <c r="D61" s="16">
+        <v>26.039818023753689</v>
+      </c>
+      <c r="E61" s="16">
+        <v>-21765.21580417292</v>
+      </c>
+      <c r="F61" s="17">
+        <v>-4250.9964143889756</v>
+      </c>
+      <c r="G61" s="17">
+        <v>309317.9523927964</v>
+      </c>
+      <c r="H61" s="17">
+        <v>1583716.2231297221</v>
+      </c>
+      <c r="I61" s="17">
+        <v>1166205.1375903317</v>
+      </c>
+      <c r="J61" s="17">
+        <v>1740735.6492126763</v>
+      </c>
+      <c r="K61" s="17">
+        <v>574530.51162234461</v>
+      </c>
+      <c r="L61" s="16">
+        <v>157019.42608295428</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,10 +70,6 @@
   </si>
   <si>
     <t>回收资金</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -453,7 +449,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -630,6 +626,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -639,7 +638,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -815,6 +814,9 @@
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
                 <c:pt idx="58">
+                  <c:v>1166205.1375903317</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
               </c:numCache>
@@ -858,7 +860,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1035,6 +1037,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1044,7 +1049,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1221,6 +1226,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>1740735.6492126763</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1668086.8606567651</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1263,7 +1271,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1440,6 +1448,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1449,7 +1460,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1626,6 +1637,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>574530.51162234461</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>501881.72306643333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1647,11 +1661,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="403014400"/>
-        <c:axId val="403017728"/>
+        <c:axId val="92055040"/>
+        <c:axId val="92066176"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="403014400"/>
+        <c:axId val="92055040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1694,14 +1708,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403017728"/>
+        <c:crossAx val="92066176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="403017728"/>
+        <c:axId val="92066176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1752,7 +1766,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="403014400"/>
+        <c:crossAx val="92055040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1943,7 +1957,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2120,6 +2134,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>-21765.21580417292</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-17431.418359027382</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2134,8 +2151,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="474839296"/>
-        <c:axId val="474837376"/>
+        <c:axId val="529156352"/>
+        <c:axId val="529154816"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2160,7 +2177,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2337,6 +2354,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2346,7 +2366,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="59"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2523,6 +2543,9 @@
                 </c:pt>
                 <c:pt idx="58">
                   <c:v>5.1200268554687502</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.8851591796875002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2539,11 +2562,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="474810240"/>
-        <c:axId val="474829184"/>
+        <c:axId val="428091648"/>
+        <c:axId val="433296128"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="474810240"/>
+        <c:axId val="428091648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2586,14 +2609,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474829184"/>
+        <c:crossAx val="433296128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="474829184"/>
+        <c:axId val="433296128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2644,12 +2667,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474810240"/>
+        <c:crossAx val="428091648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="474837376"/>
+        <c:axId val="529154816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2686,12 +2709,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474839296"/>
+        <c:crossAx val="529156352"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="474839296"/>
+        <c:axId val="529156352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2700,7 +2723,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="474837376"/>
+        <c:crossAx val="529154816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3109,7 +3132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3186,7 +3209,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3238,13 +3261,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="R3" s="26" t="s">
         <v>13</v>
-      </c>
-      <c r="R3" s="26" t="s">
-        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3256,10 +3279,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="W3" s="26" t="s">
         <v>15</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5698,6 +5721,44 @@
       </c>
       <c r="L61" s="16">
         <v>157019.42608295428</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A62" s="14">
+        <v>46112</v>
+      </c>
+      <c r="B62" s="15">
+        <v>4.8851591796875002</v>
+      </c>
+      <c r="C62" s="15">
+        <v>30.549999239999998</v>
+      </c>
+      <c r="D62" s="16">
+        <v>26.136981933917117</v>
+      </c>
+      <c r="E62" s="16">
+        <v>-17431.418359027382</v>
+      </c>
+      <c r="F62" s="17">
+        <v>-3568.2395839847445</v>
+      </c>
+      <c r="G62" s="17">
+        <v>305749.71280881169</v>
+      </c>
+      <c r="H62" s="17">
+        <v>1493636.0162147833</v>
+      </c>
+      <c r="I62" s="17">
+        <v>1166205.1375903317</v>
+      </c>
+      <c r="J62" s="17">
+        <v>1668086.8606567651</v>
+      </c>
+      <c r="K62" s="17">
+        <v>501881.72306643333</v>
+      </c>
+      <c r="L62" s="16">
+        <v>174450.84444198167</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
@@ -449,7 +449,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -629,6 +629,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -638,7 +641,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -817,6 +820,9 @@
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1166205.1375903317</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
               </c:numCache>
@@ -860,7 +866,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1040,6 +1046,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1049,7 +1058,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1229,6 +1238,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1668086.8606567651</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1870080.0799818321</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1271,7 +1283,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1451,6 +1463,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1460,7 +1475,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1640,6 +1655,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>501881.72306643333</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>703874.94239150034</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1661,11 +1679,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="92055040"/>
-        <c:axId val="92066176"/>
+        <c:axId val="444458496"/>
+        <c:axId val="444460416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="92055040"/>
+        <c:axId val="444458496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1708,14 +1726,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92066176"/>
+        <c:crossAx val="444460416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="92066176"/>
+        <c:axId val="444460416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1766,7 +1784,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92055040"/>
+        <c:crossAx val="444458496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1957,7 +1975,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2137,6 +2155,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-17431.418359027382</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-32774.923782847916</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2151,8 +2172,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="529156352"/>
-        <c:axId val="529154816"/>
+        <c:axId val="486101376"/>
+        <c:axId val="444530048"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2177,7 +2198,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2357,6 +2378,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2366,7 +2390,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2546,6 +2570,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>4.8851591796875002</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>5.5458081054687502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2562,11 +2589,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="428091648"/>
-        <c:axId val="433296128"/>
+        <c:axId val="444513664"/>
+        <c:axId val="444528512"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="428091648"/>
+        <c:axId val="444513664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2609,14 +2636,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433296128"/>
+        <c:crossAx val="444528512"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433296128"/>
+        <c:axId val="444528512"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2667,12 +2694,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="428091648"/>
+        <c:crossAx val="444513664"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="529154816"/>
+        <c:axId val="444530048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2709,12 +2736,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="529156352"/>
+        <c:crossAx val="486101376"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="529156352"/>
+        <c:axId val="486101376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2723,7 +2750,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="529154816"/>
+        <c:crossAx val="444530048"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3132,7 +3159,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -5761,6 +5788,44 @@
         <v>174450.84444198167</v>
       </c>
     </row>
+    <row r="63" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A63" s="14">
+        <v>46142</v>
+      </c>
+      <c r="B63" s="15">
+        <v>5.5458081054687502</v>
+      </c>
+      <c r="C63" s="15">
+        <v>34.549999239999998</v>
+      </c>
+      <c r="D63" s="16">
+        <v>26.252550181051159</v>
+      </c>
+      <c r="E63" s="16">
+        <v>-32774.923782847916</v>
+      </c>
+      <c r="F63" s="17">
+        <v>-5909.8553645461325</v>
+      </c>
+      <c r="G63" s="17">
+        <v>299839.85744426557</v>
+      </c>
+      <c r="H63" s="17">
+        <v>1662854.3117570025</v>
+      </c>
+      <c r="I63" s="17">
+        <v>1166205.1375903317</v>
+      </c>
+      <c r="J63" s="17">
+        <v>1870080.0799818321</v>
+      </c>
+      <c r="K63" s="17">
+        <v>703874.94239150034</v>
+      </c>
+      <c r="L63" s="16">
+        <v>207225.76822482958</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
+++ b/lai/valuationquan/szseinnovation100index/szseinnovation100indexmodel2cn.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -70,6 +70,10 @@
   </si>
   <si>
     <t>回收资金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -449,7 +453,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -632,6 +636,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -641,7 +648,7 @@
               <c:f>'模型二 (1)PE副本'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -823,6 +830,9 @@
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1166205.1375903317</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1166205.1375903317</c:v>
                 </c:pt>
               </c:numCache>
@@ -866,7 +876,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1049,6 +1059,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1058,7 +1071,7 @@
               <c:f>'模型二 (1)PE副本'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1241,6 +1254,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1870080.0799818321</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1997480.5420668602</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1283,7 +1299,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -1466,6 +1482,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1475,7 +1494,7 @@
               <c:f>'模型二 (1)PE副本'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1658,6 +1677,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>703874.94239150034</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>831275.40447652852</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1679,11 +1701,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444458496"/>
-        <c:axId val="444460416"/>
+        <c:axId val="443120256"/>
+        <c:axId val="443128064"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444458496"/>
+        <c:axId val="443120256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1726,14 +1748,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444460416"/>
+        <c:crossAx val="443128064"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444460416"/>
+        <c:axId val="443128064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1784,7 +1806,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444458496"/>
+        <c:crossAx val="443120256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1975,7 +1997,7 @@
               <c:f>'模型二 (1)PE副本'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2158,6 +2180,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-32774.923782847916</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-36057.366675283578</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2172,8 +2197,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="486101376"/>
-        <c:axId val="444530048"/>
+        <c:axId val="445485440"/>
+        <c:axId val="445479552"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2198,7 +2223,7 @@
               <c:f>'模型二 (1)PE副本'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44316</c:v>
                 </c:pt>
@@ -2381,6 +2406,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2390,7 +2418,7 @@
               <c:f>'模型二 (1)PE副本'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>4.7860299999999993</c:v>
                 </c:pt>
@@ -2573,6 +2601,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>5.5458081054687502</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.970703125</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2589,11 +2620,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="444513664"/>
-        <c:axId val="444528512"/>
+        <c:axId val="445450880"/>
+        <c:axId val="445477248"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="444513664"/>
+        <c:axId val="445450880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2636,14 +2667,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444528512"/>
+        <c:crossAx val="445477248"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="444528512"/>
+        <c:axId val="445477248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2694,12 +2725,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="444513664"/>
+        <c:crossAx val="445450880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="444530048"/>
+        <c:axId val="445479552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2736,12 +2767,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="486101376"/>
+        <c:crossAx val="445485440"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="486101376"/>
+        <c:axId val="445485440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2750,7 +2781,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="444530048"/>
+        <c:crossAx val="445479552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3159,7 +3190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3236,7 +3267,7 @@
         <v>3950</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4">
@@ -3288,13 +3319,13 @@
       </c>
       <c r="M3" s="6"/>
       <c r="P3" s="25" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q3" s="26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R3" s="26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S3" s="26" t="s">
         <v>9</v>
@@ -3306,10 +3337,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y3" s="19">
         <v>44561</v>
@@ -5824,6 +5855,44 @@
       </c>
       <c r="L63" s="16">
         <v>207225.76822482958</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A64" s="14">
+        <v>46171</v>
+      </c>
+      <c r="B64" s="15">
+        <v>5.970703125</v>
+      </c>
+      <c r="C64" s="15">
+        <v>35.509998320000001</v>
+      </c>
+      <c r="D64" s="16">
+        <v>26.381551060434539</v>
+      </c>
+      <c r="E64" s="16">
+        <v>-36057.366675283578</v>
+      </c>
+      <c r="F64" s="17">
+        <v>-6039.048654807063</v>
+      </c>
+      <c r="G64" s="17">
+        <v>293800.80878945848</v>
+      </c>
+      <c r="H64" s="17">
+        <v>1754197.4071667471</v>
+      </c>
+      <c r="I64" s="17">
+        <v>1166205.1375903317</v>
+      </c>
+      <c r="J64" s="17">
+        <v>1997480.5420668602</v>
+      </c>
+      <c r="K64" s="17">
+        <v>831275.40447652852</v>
+      </c>
+      <c r="L64" s="16">
+        <v>243283.13490011316</v>
       </c>
     </row>
   </sheetData>
